--- a/content/source/biology.xlsx
+++ b/content/source/biology.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cards" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Cards" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Questions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cards'!$A$1:$E$161</definedName>
@@ -528,7 +528,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>H-bonds hold the double helix together — weak but specific.</t>
+          <t>H-bonds hold the double helix together. Weak but specific.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Thin moist membrane, huge area — exchange happens nowhere else.</t>
+          <t>Thin moist membrane, huge area. Exchange happens nowhere else.</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>Happens in cytoplasm — solution-phase chemistry, no surface involved.</t>
+          <t>Happens in cytoplasm. Solution-phase chemistry, no surface involved.</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>Offspring stays attached to the mother — the opposite of dispersal.</t>
+          <t>Offspring stays attached to the mother. The opposite of dispersal.</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>Corals don't move — no locomotion to contribute to anything.</t>
+          <t>Corals don't move. No locomotion to contribute to anything.</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Whole ecosystems thrive in total darkness — light isn't essential everywhere.</t>
+          <t>Whole ecosystems thrive in total darkness. Light isn't essential everywhere.</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>They make light, don't depend on it — keyword trap.</t>
+          <t>They make light, don't depend on it. Keyword trap.</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>One shape fits one substrate — extreme specificity.</t>
+          <t>One shape fits one substrate. Extreme specificity.</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>One cell type can become many — maximum versatility.</t>
+          <t>One cell type can become many. Maximum versatility.</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>A universal core process — neither specific nor versatile in the relevant sense.</t>
+          <t>A universal core process. Neither specific nor versatile in the relevant sense.</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Visualizes proteins floating in a lipid sea — guides thinking.</t>
+          <t>Visualizes proteins floating in a lipid sea. Guides thinking.</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>This is observation, not modeling — the opposite approach.</t>
+          <t>This is observation, not modeling. The opposite approach.</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>All active sites occupied — rate can't go higher.</t>
+          <t>All active sites occupied. Rate can't go higher.</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Four binding sites per molecule — a hard ceiling.</t>
+          <t>Four binding sites per molecule. A hard ceiling.</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Large mass, low SA:V — heat is lost slowly.</t>
+          <t>Large mass, low SA:V. Heat is lost slowly.</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
@@ -2003,7 +2003,7 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>Produces identical daughter cells — no differentiation at all.</t>
+          <t>Produces identical daughter cells. No differentiation at all.</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>Unicellular — no multicellular problem to solve.</t>
+          <t>Unicellular. No multicellular problem to solve.</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>This is transport — sits between exchange and metabolism, is neither.</t>
+          <t>This is transport. Sits between exchange and metabolism, is neither.</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="D76" s="3" t="inlineStr">
         <is>
-          <t>This is activation, not inhibition — the opposite.</t>
+          <t>This is activation, not inhibition. The opposite.</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="D81" s="3" t="inlineStr">
         <is>
-          <t>Genetic sameness — the opposite of diversification.</t>
+          <t>Genetic sameness. The opposite of diversification.</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="D86" s="3" t="inlineStr">
         <is>
-          <t>Different molecules, different problem — atmospheric but unrelated.</t>
+          <t>Different molecules, different problem. Atmospheric but unrelated.</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>Passive movement down a gradient — no energy transformed.</t>
+          <t>Passive movement down a gradient. No energy transformed.</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Each new strand templated from an original — sequence preserved.</t>
+          <t>Each new strand templated from an original. Sequence preserved.</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="D96" s="3" t="inlineStr">
         <is>
-          <t>Generates variation — the opposite of continuity.</t>
+          <t>Generates variation. The opposite of continuity.</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -2903,7 +2903,7 @@
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>RNA polymerase only adds at the 3' end — direction is built in.</t>
+          <t>RNA polymerase only adds at the 3' end. Direction is built in.</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="D101" s="3" t="inlineStr">
         <is>
-          <t>Direction depends entirely on the gradient — no inherent direction.</t>
+          <t>Direction depends entirely on the gradient. No inherent direction.</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>Intraspecific cooperation — same species working as one.</t>
+          <t>Intraspecific cooperation. Same species working as one.</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>Interspecific mutualism — different species exchanging resources.</t>
+          <t>Interspecific mutualism. Different species exchanging resources.</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="D106" s="3" t="inlineStr">
         <is>
-          <t>No interaction between organisms at all — wrong scale.</t>
+          <t>No interaction between organisms at all. Wrong scale.</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="D111" s="3" t="inlineStr">
         <is>
-          <t>Cooperation between species — not a competition mechanism at all.</t>
+          <t>Cooperation between species. Not a competition mechanism at all.</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>Humans chose the traits — deliberate, artificial selection.</t>
+          <t>Humans chose the traits. Deliberate, artificial selection.</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>No human hand — pure natural selection.</t>
+          <t>No human hand. Pure natural selection.</t>
         </is>
       </c>
       <c r="E113" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="D116" s="3" t="inlineStr">
         <is>
-          <t>A neutral biological process — doesn't engage the distinction.</t>
+          <t>A neutral biological process. Doesn't engage the distinction.</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="D121" s="3" t="inlineStr">
         <is>
-          <t>A number, not a timescale — not even time.</t>
+          <t>A number, not a timescale. Not even time.</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="D126" s="3" t="inlineStr">
         <is>
-          <t>That's a census, not sampling — the opposite approach.</t>
+          <t>That's a census, not sampling. The opposite approach.</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="D127" s="2" t="inlineStr">
         <is>
-          <t>Every chromosome becomes two sister chromatids — exact doubling.</t>
+          <t>Every chromosome becomes two sister chromatids. Exact doubling.</t>
         </is>
       </c>
       <c r="E127" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="D128" s="2" t="inlineStr">
         <is>
-          <t>2n becomes n — halving is the defining feature.</t>
+          <t>2n becomes n. Halving is the defining feature.</t>
         </is>
       </c>
       <c r="E128" s="2" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="D133" s="2" t="inlineStr">
         <is>
-          <t>Leaves make more than they use — growing tissues need the surplus.</t>
+          <t>Leaves make more than they use. Growing tissues need the surplus.</t>
         </is>
       </c>
       <c r="E133" s="2" t="inlineStr">
@@ -4003,7 +4003,7 @@
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>Set by alleles at conception — temperature has no effect.</t>
+          <t>Set by alleles at conception. Temperature has no effect.</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="D142" s="2" t="inlineStr">
         <is>
-          <t>Every known cell uses ATP — bacteria, plants, animals, fungi.</t>
+          <t>Every known cell uses ATP. Bacteria, plants, animals, fungi.</t>
         </is>
       </c>
       <c r="E142" s="2" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="D146" s="3" t="inlineStr">
         <is>
-          <t>Only fungi and arthropods — not universal at all.</t>
+          <t>Only fungi and arthropods. Not universal at all.</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
@@ -4178,7 +4178,7 @@
       </c>
       <c r="D148" s="2" t="inlineStr">
         <is>
-          <t>All life is cells — sweeping, testable, predictive.</t>
+          <t>All life is cells. Sweeping, testable, predictive.</t>
         </is>
       </c>
       <c r="E148" s="2" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D151" s="3" t="inlineStr">
         <is>
-          <t>That's a list, not a theory — no explanatory power.</t>
+          <t>That's a list, not a theory. No explanatory power.</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="D156" s="3" t="inlineStr">
         <is>
-          <t>Organism-level mortality — doesn't determine whether a species persists.</t>
+          <t>Organism-level mortality. Doesn't determine whether a species persists.</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
@@ -4403,7 +4403,7 @@
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>Many genes and environment combine — any value possible.</t>
+          <t>Many genes and environment combine. Any value possible.</t>
         </is>
       </c>
       <c r="E157" s="2" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Mendel's pea shape — round or wrinkled</t>
+          <t>Mendel's pea shape. Round or wrinkled</t>
         </is>
       </c>
       <c r="D160" s="2" t="inlineStr">
